--- a/data/trans_orig/P36B12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B12-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141970</t>
+          <t>141301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187150</t>
+          <t>185054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125640</t>
+          <t>123533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168780</t>
+          <t>167775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275801</t>
+          <t>279902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>338812</t>
+          <t>341036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>372003</t>
+          <t>374706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>424688</t>
+          <t>427017</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>422451</t>
+          <t>424907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>475678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>812730</t>
+          <t>812448</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>886127</t>
+          <t>882341</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80172</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117072</t>
+          <t>115677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64679</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98885</t>
+          <t>99632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151589</t>
+          <t>154592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201750</t>
+          <t>203681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>34553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30957</t>
+          <t>30387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56751</t>
+          <t>54824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>46317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77286</t>
+          <t>79758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166406</t>
+          <t>166248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214406</t>
+          <t>216859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117164</t>
+          <t>118282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>162996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300002</t>
+          <t>296342</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372993</t>
+          <t>368143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>469106</t>
+          <t>468818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>530415</t>
+          <t>531707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550601</t>
+          <t>552539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>610681</t>
+          <t>609710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1037073</t>
+          <t>1031968</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1125495</t>
+          <t>1123550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197744</t>
+          <t>201443</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254621</t>
+          <t>256905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163646</t>
+          <t>163642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216503</t>
+          <t>214123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377356</t>
+          <t>376718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>452216</t>
+          <t>455968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54188</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>23561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28341</t>
+          <t>27025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53440</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>98669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140967</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102261</t>
+          <t>102398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140785</t>
+          <t>141475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215099</t>
+          <t>210625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270449</t>
+          <t>270251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>370467</t>
+          <t>374165</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>424501</t>
+          <t>424198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>390749</t>
+          <t>390640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>438008</t>
+          <t>440608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>775107</t>
+          <t>771943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>848505</t>
+          <t>847480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112854</t>
+          <t>114637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156713</t>
+          <t>157593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98588</t>
+          <t>98180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>137378</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>221788</t>
+          <t>223639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281675</t>
+          <t>280689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>19913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>40057</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44211</t>
+          <t>44091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75073</t>
+          <t>75002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166824</t>
+          <t>168001</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215281</t>
+          <t>215820</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>189355</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>240135</t>
+          <t>239052</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>367687</t>
+          <t>372400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437712</t>
+          <t>439680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>464042</t>
+          <t>466507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>526446</t>
+          <t>526825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>531480</t>
+          <t>530802</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>593609</t>
+          <t>594863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1008329</t>
+          <t>1011732</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1101603</t>
+          <t>1099882</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179331</t>
+          <t>180196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230513</t>
+          <t>229375</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185871</t>
+          <t>184565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>239222</t>
+          <t>238557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>378834</t>
+          <t>378156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>447775</t>
+          <t>447416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>33699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31316</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31134</t>
+          <t>33068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59000</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>60742</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93886</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>126857</t>
+          <t>125462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>155097</t>
+          <t>157909</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>212057</t>
+          <t>207545</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>613340</t>
+          <t>614042</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>706835</t>
+          <t>709478</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>573676</t>
+          <t>577783</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>662268</t>
+          <t>664724</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1219561</t>
+          <t>1215180</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1345986</t>
+          <t>1341065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1738550</t>
+          <t>1735999</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1854640</t>
+          <t>1847720</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1953737</t>
+          <t>1955627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2064585</t>
+          <t>2064424</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3722774</t>
+          <t>3723715</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3880925</t>
+          <t>3885786</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>610570</t>
+          <t>620467</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>711059</t>
+          <t>711264</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>546641</t>
+          <t>548900</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>638788</t>
+          <t>640127</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1191376</t>
+          <t>1192762</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1325381</t>
+          <t>1320768</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>95522</t>
+          <t>96812</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>62340</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>102838</t>
+          <t>100901</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>149894</t>
+          <t>148019</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35671</t>
+          <t>35831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33035</t>
+          <t>32910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>60358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120642</t>
+          <t>121044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163260</t>
+          <t>166037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122157</t>
+          <t>122459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167866</t>
+          <t>166826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257353</t>
+          <t>253253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>320942</t>
+          <t>316632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>361894</t>
+          <t>364418</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>414591</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385993</t>
+          <t>384809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>436811</t>
+          <t>438757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>765637</t>
+          <t>766866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>837284</t>
+          <t>847098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114091</t>
+          <t>112897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155980</t>
+          <t>155529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88691</t>
+          <t>89233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130134</t>
+          <t>130337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>217543</t>
+          <t>212873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274448</t>
+          <t>273775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>27700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28466</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56022</t>
+          <t>55423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132730</t>
+          <t>132974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182251</t>
+          <t>179595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131648</t>
+          <t>129444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178242</t>
+          <t>177267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279241</t>
+          <t>276744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346369</t>
+          <t>341669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>547788</t>
+          <t>547490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>614523</t>
+          <t>615512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>562809</t>
+          <t>561011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>629040</t>
+          <t>627874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1134263</t>
+          <t>1134202</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1223724</t>
+          <t>1227326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216729</t>
+          <t>218530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>272972</t>
+          <t>275990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218353</t>
+          <t>221081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277195</t>
+          <t>277581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448307</t>
+          <t>447493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528539</t>
+          <t>524426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>39464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57297</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77318</t>
+          <t>74417</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115155</t>
+          <t>112620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101761</t>
+          <t>103201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146234</t>
+          <t>145872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190531</t>
+          <t>191334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249855</t>
+          <t>250241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>442064</t>
+          <t>441144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>496826</t>
+          <t>497596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>442692</t>
+          <t>440747</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>498573</t>
+          <t>498633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>900628</t>
+          <t>896970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>982037</t>
+          <t>979895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>129292</t>
+          <t>130848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178195</t>
+          <t>177974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126666</t>
+          <t>122977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171266</t>
+          <t>169837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>268235</t>
+          <t>268873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333399</t>
+          <t>333281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24044</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>28406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51329</t>
+          <t>50416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>117411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>161823</t>
+          <t>159122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183127</t>
+          <t>183291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>235342</t>
+          <t>238728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,47 +6584,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>22,8%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>348278</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>315646</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>384756</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>17,49%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>348278</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>316460</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>384206</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>469858</t>
+          <t>473141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>535459</t>
+          <t>535955</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>514891</t>
+          <t>512610</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>581430</t>
+          <t>582519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1007576</t>
+          <t>1007672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1094369</t>
+          <t>1101190</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>238592</t>
+          <t>235848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>295362</t>
+          <t>295476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222887</t>
+          <t>225883</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>278734</t>
+          <t>281917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>479920</t>
+          <t>478643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>555925</t>
+          <t>557755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29629</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28126</t>
+          <t>28940</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52807</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>63126</t>
+          <t>64255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>100707</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>67970</t>
+          <t>65864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>104021</t>
+          <t>102106</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>139349</t>
+          <t>139220</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192155</t>
+          <t>189290</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>489294</t>
+          <t>483609</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>576511</t>
+          <t>575256</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>585754</t>
+          <t>585989</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>680146</t>
+          <t>678392</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1098845</t>
+          <t>1095668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1227009</t>
+          <t>1227649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1880380</t>
+          <t>1884320</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2006785</t>
+          <t>2001515</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1968050</t>
+          <t>1963012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2093340</t>
+          <t>2083523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3889458</t>
+          <t>3867941</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4050180</t>
+          <t>4059204</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>746749</t>
+          <t>748240</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>850652</t>
+          <t>847920</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>700288</t>
+          <t>705356</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>800740</t>
+          <t>811917</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1481496</t>
+          <t>1470933</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1620949</t>
+          <t>1626480</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48631</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>80112</t>
+          <t>81864</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38979</t>
+          <t>40536</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>68296</t>
+          <t>71373</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>96514</t>
+          <t>96574</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>139622</t>
+          <t>142893</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>48801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86059</t>
+          <t>87635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76557</t>
+          <t>77128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114908</t>
+          <t>114249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140583</t>
+          <t>139616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186502</t>
+          <t>187957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>371875</t>
+          <t>372824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>423465</t>
+          <t>425049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377918</t>
+          <t>378440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>429473</t>
+          <t>430151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>763533</t>
+          <t>768649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>835487</t>
+          <t>841291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148735</t>
+          <t>146495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>194579</t>
+          <t>191495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122981</t>
+          <t>122770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167204</t>
+          <t>165100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286516</t>
+          <t>283174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348742</t>
+          <t>346289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>26697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>31897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84391</t>
+          <t>84001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124887</t>
+          <t>123656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106839</t>
+          <t>103458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150992</t>
+          <t>147892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201162</t>
+          <t>200167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259070</t>
+          <t>258338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>584463</t>
+          <t>584694</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>648084</t>
+          <t>649699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>590582</t>
+          <t>592808</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>655887</t>
+          <t>655571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1196804</t>
+          <t>1199557</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1293463</t>
+          <t>1286942</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225404</t>
+          <t>224014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280616</t>
+          <t>279375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224920</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280318</t>
+          <t>279318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>462158</t>
+          <t>462778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>545819</t>
+          <t>537455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>18967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41545</t>
+          <t>40684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>64079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>31866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100032</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142404</t>
+          <t>141435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118348</t>
+          <t>118533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162891</t>
+          <t>162540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226487</t>
+          <t>228451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287787</t>
+          <t>290420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>353838</t>
+          <t>358020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>412706</t>
+          <t>411993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>380036</t>
+          <t>381305</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>439006</t>
+          <t>434864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>750930</t>
+          <t>752585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>832265</t>
+          <t>832315</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195722</t>
+          <t>197217</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>248489</t>
+          <t>249554</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>184056</t>
+          <t>183492</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236092</t>
+          <t>232285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>394710</t>
+          <t>395427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>465919</t>
+          <t>468013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,82 +10078,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>16248</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10185</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>27393</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>35005</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>23859</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>48229</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>16248</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>9377</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>27146</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>35005</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>24230</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>47729</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93390</t>
+          <t>91262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130145</t>
+          <t>134133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128616</t>
+          <t>128321</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174338</t>
+          <t>174377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232419</t>
+          <t>229943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>293706</t>
+          <t>294198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>532418</t>
+          <t>532127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>591160</t>
+          <t>590801</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>591785</t>
+          <t>591092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>654279</t>
+          <t>652500</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1141113</t>
+          <t>1141610</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1227554</t>
+          <t>1230388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>191483</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>245466</t>
+          <t>244221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202332</t>
+          <t>201199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254408</t>
+          <t>256363</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>405817</t>
+          <t>409742</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>482855</t>
+          <t>482431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37964</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32409</t>
+          <t>33332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60213</t>
+          <t>60630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>53254</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87701</t>
+          <t>87763</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>45836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77332</t>
+          <t>77103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>108643</t>
+          <t>107830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>153432</t>
+          <t>153118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>365930</t>
+          <t>364510</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>445258</t>
+          <t>442895</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>467033</t>
+          <t>473623</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>555735</t>
+          <t>555999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>851414</t>
+          <t>849574</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>972780</t>
+          <t>966743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1900974</t>
+          <t>1902659</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2022443</t>
+          <t>2014539</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1999443</t>
+          <t>2000728</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2119780</t>
+          <t>2119240</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3941480</t>
+          <t>3942108</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4109553</t>
+          <t>4107352</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>809678</t>
+          <t>811488</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>914908</t>
+          <t>914597</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>778463</t>
+          <t>778797</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>887145</t>
+          <t>882872</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1628196</t>
+          <t>1621009</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1769683</t>
+          <t>1771680</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64282</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101113</t>
+          <t>100438</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>51036</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>85000</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>124108</t>
+          <t>124722</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>171615</t>
+          <t>170351</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -11654,17 +11654,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>20742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>46784</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33518</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63947</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58842</t>
+          <t>61537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>73837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>104520</t>
+          <t>108321</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88411</t>
+          <t>91621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125436</t>
+          <t>128788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399612</t>
+          <t>426536</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>372489</t>
+          <t>395586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>426537</t>
+          <t>453253</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>486670</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>435905</t>
+          <t>464837</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>473960</t>
+          <t>506931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>853439</t>
+          <t>913205</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>823146</t>
+          <t>876087</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>887584</t>
+          <t>945761</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>159825</t>
+          <t>183021</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137683</t>
+          <t>157833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187512</t>
+          <t>209136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>145346</t>
+          <t>164651</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128767</t>
+          <t>145256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163476</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>305171</t>
+          <t>347671</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276484</t>
+          <t>317217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335661</t>
+          <t>379811</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>40999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>60548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674818</t>
+          <t>732165</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>674818</t>
+          <t>732165</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>674818</t>
+          <t>732165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1310260</t>
+          <t>1422874</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1310260</t>
+          <t>1422874</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1310260</t>
+          <t>1422874</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,67 +12336,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9617</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4967</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18336</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8239</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3788</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16847</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71533</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104109</t>
+          <t>87620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66453</t>
+          <t>71401</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>59242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79200</t>
+          <t>84790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>137986</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96513</t>
+          <t>121845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170474</t>
+          <t>163211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>518405</t>
+          <t>576206</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261634</t>
+          <t>544117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666180</t>
+          <t>618154</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>583353</t>
+          <t>636588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>556729</t>
+          <t>606521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>612969</t>
+          <t>665378</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1101759</t>
+          <t>1212794</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>724329</t>
+          <t>1166090</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1258213</t>
+          <t>1261556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>323443</t>
+          <t>358042</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148968</t>
+          <t>322334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>422369</t>
+          <t>392526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>276812</t>
+          <t>322521</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251237</t>
+          <t>294841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302577</t>
+          <t>352231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>680564</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395249</t>
+          <t>636494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>691992</t>
+          <t>726618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>266841</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>743369</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>290090</t>
+          <t>61816</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>47242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878194</t>
+          <t>80637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29613</t>
+          <t>28675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87442</t>
+          <t>91414</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67864</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110150</t>
+          <t>115772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>112014</t>
+          <t>122914</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55273</t>
+          <t>106006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151513</t>
+          <t>144254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>199457</t>
+          <t>214328</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132573</t>
+          <t>189590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240034</t>
+          <t>244626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>353452</t>
+          <t>397754</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>322961</t>
+          <t>365128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>384525</t>
+          <t>434141</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>356807</t>
+          <t>383268</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183748</t>
+          <t>356372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>477496</t>
+          <t>410267</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>710259</t>
+          <t>781022</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>481137</t>
+          <t>736438</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>831503</t>
+          <t>822931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>225504</t>
+          <t>266756</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>198610</t>
+          <t>236480</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>255379</t>
+          <t>299763</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>433529</t>
+          <t>265479</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>279228</t>
+          <t>240596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>673588</t>
+          <t>291492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>659033</t>
+          <t>532235</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>503544</t>
+          <t>495347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>971701</t>
+          <t>570315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>58102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>33493</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37848</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>71860</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74949</t>
+          <t>96996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>16240</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28637</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>24348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>111793</t>
+          <t>116289</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>96257</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>139512</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>133256</t>
+          <t>136381</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105741</t>
+          <t>118764</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158130</t>
+          <t>156558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>245049</t>
+          <t>252670</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208908</t>
+          <t>224890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275733</t>
+          <t>281299</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>505270</t>
+          <t>523742</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>466990</t>
+          <t>489832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>536796</t>
+          <t>556455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>621594</t>
+          <t>588509</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>577806</t>
+          <t>555358</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>716030</t>
+          <t>615844</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1126864</t>
+          <t>1112252</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1072655</t>
+          <t>1066762</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1236079</t>
+          <t>1160383</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>258026</t>
+          <t>290975</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231274</t>
+          <t>261379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>288359</t>
+          <t>325757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>293724</t>
+          <t>332770</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>233782</t>
+          <t>308046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>326622</t>
+          <t>364124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>551750</t>
+          <t>623745</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>485758</t>
+          <t>587524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>594027</t>
+          <t>667200</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29257</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56991</t>
+          <t>64446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>27810</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36876</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>67795</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>67748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84106</t>
+          <t>104860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1094367</t>
+          <t>1118473</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1094367</t>
+          <t>1118473</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1094367</t>
+          <t>1118473</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2020193</t>
+          <t>2107601</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2020193</t>
+          <t>2107601</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2020193</t>
+          <t>2107601</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>37140</t>
+          <t>40213</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52238</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>45583</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27382</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75933</t>
+          <t>85796</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60036</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>98887</t>
+          <t>105601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>316448</t>
+          <t>323953</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>241075</t>
+          <t>289498</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>360485</t>
+          <t>361199</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>370565</t>
+          <t>392233</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>301575</t>
+          <t>359436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>412405</t>
+          <t>425012</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>687013</t>
+          <t>716186</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>589545</t>
+          <t>667319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>757288</t>
+          <t>767423</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1776740</t>
+          <t>1924238</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1354957</t>
+          <t>1859154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1933038</t>
+          <t>1989530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2015580</t>
+          <t>2095035</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1630846</t>
+          <t>2040813</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2166213</t>
+          <t>2147059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3792320</t>
+          <t>4019273</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3340500</t>
+          <t>3934497</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4062635</t>
+          <t>4102955</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>966798</t>
+          <t>1098795</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>731338</t>
+          <t>1032509</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1063723</t>
+          <t>1157319</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1149411</t>
+          <t>1085420</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>981268</t>
+          <t>1037487</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1650267</t>
+          <t>1135641</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2116209</t>
+          <t>2184215</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1894388</t>
+          <t>2109088</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2644859</t>
+          <t>2266845</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>361686</t>
+          <t>144629</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>117395</t>
+          <t>119033</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1146900</t>
+          <t>173683</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>86309</t>
+          <t>115462</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>68518</t>
+          <t>97998</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>104506</t>
+          <t>137982</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>447995</t>
+          <t>260091</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>200975</t>
+          <t>224214</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1320683</t>
+          <t>295941</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3458812</t>
+          <t>3531828</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3458812</t>
+          <t>3531828</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3458812</t>
+          <t>3531828</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3660657</t>
+          <t>3733734</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3660657</t>
+          <t>3733734</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3660657</t>
+          <t>3733734</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7119470</t>
+          <t>7265562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7119470</t>
+          <t>7265562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7119470</t>
+          <t>7265562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
